--- a/outputs/q4/solution_audit.xlsx
+++ b/outputs/q4/solution_audit.xlsx
@@ -457,7 +457,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>102294.2731529621</v>
+        <v>75495.42500039333</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -477,7 +477,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>99944.32777777777</v>
+        <v>71307.92012941677</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>0.9999948144313333</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -517,7 +517,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>812832.0000000002</v>
+        <v>588085.5399541908</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -537,7 +537,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4284.770689200003</v>
+        <v>1848.313237059225</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
